--- a/rq3-survey-analysis-tool/data/source/Final_50_Claims_Public.xlsx
+++ b/rq3-survey-analysis-tool/data/source/Final_50_Claims_Public.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aakashdoli/Master Thesis/RQ3 Survey Analysis Tool/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE2986D-FCFB-CC48-98F0-8800A7A39525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2ACC209-D2C4-6B44-8346-5E65B569935F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
